--- a/NN/reports/optimization_report.xlsx
+++ b/NN/reports/optimization_report.xlsx
@@ -7,7 +7,10 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Recommendations" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Objective Forecasts" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Historical Limits" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Summary" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -29,12 +32,17 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9EAD3"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -57,7 +65,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -425,61 +433,1102 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="25" customWidth="1" min="8" max="8"/>
+    <col width="29" customWidth="1" min="9" max="9"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>Method</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>reason</t>
+          <t>Variable</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>required_control_variables</t>
+          <t>Current Value</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>required_objectives</t>
+          <t>Recommended Value</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>created_at_utc</t>
+          <t>Change</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Expected Improvement</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Expected Improvement %</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Current Objective Score</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Recommended Objective Score</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>Bayesian Optimization</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Missing required columns: lime_milk_baume</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
+          <t>lime_milk_baume</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>11</v>
+      </c>
+      <c r="D2" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.2810184079122604</v>
+      </c>
+      <c r="G2" t="n">
+        <v>49.03487636062059</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.573099044536275</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.2920806366240146</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Bayesian Optimization</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>lime_alkalinity</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>9.380000000000001</v>
+      </c>
+      <c r="D3" t="n">
+        <v>4</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-5.380000000000001</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.2810184079122604</v>
+      </c>
+      <c r="G3" t="n">
+        <v>49.03487636062059</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.573099044536275</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.2920806366240146</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Bayesian Optimization</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>co2_percent</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>7.42</v>
+      </c>
+      <c r="D4" t="n">
+        <v>5.89</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-1.53</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.2810184079122604</v>
+      </c>
+      <c r="G4" t="n">
+        <v>49.03487636062059</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.573099044536275</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.2920806366240146</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Bayesian Optimization</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>carbonated_pH</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>7.63</v>
+      </c>
+      <c r="D5" t="n">
+        <v>8.529999999999999</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.8999999999999995</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.2810184079122604</v>
+      </c>
+      <c r="G5" t="n">
+        <v>49.03487636062059</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.573099044536275</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.2920806366240146</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Bayesian Optimization</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>sulphited_pH</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>6.95</v>
+      </c>
+      <c r="D6" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-0.7000000000000002</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.2810184079122604</v>
+      </c>
+      <c r="G6" t="n">
+        <v>49.03487636062059</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.573099044536275</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.2920806366240146</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Bayesian Optimization</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>sulphited_brix</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>61.67</v>
+      </c>
+      <c r="D7" t="n">
+        <v>52.02</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-9.649999999999999</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.2810184079122604</v>
+      </c>
+      <c r="G7" t="n">
+        <v>49.03487636062059</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.573099044536275</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.2920806366240146</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Bayesian Optimization</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>standard_liquor_pH</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>7.15</v>
+      </c>
+      <c r="D8" t="n">
+        <v>5.93</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-1.220000000000001</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.2810184079122604</v>
+      </c>
+      <c r="G8" t="n">
+        <v>49.03487636062059</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.573099044536275</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.2920806366240146</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Bayesian Optimization</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>standard_liquor_brix</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>54.72</v>
+      </c>
+      <c r="D9" t="n">
+        <v>48.7</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-6.019999999999996</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.2810184079122604</v>
+      </c>
+      <c r="G9" t="n">
+        <v>49.03487636062059</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.573099044536275</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.2920806366240146</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Differential Evolution</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>lime_milk_baume</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>11</v>
+      </c>
+      <c r="D10" t="n">
+        <v>788.1001220087167</v>
+      </c>
+      <c r="E10" t="n">
+        <v>777.1001220087167</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.5020118909237635</v>
+      </c>
+      <c r="G10" t="n">
+        <v>87.59600905110008</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.573099044536275</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.07108715361251147</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Differential Evolution</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>lime_alkalinity</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>9.380000000000001</v>
+      </c>
+      <c r="D11" t="n">
+        <v>9.985131812787353</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.6051318127873522</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.5020118909237635</v>
+      </c>
+      <c r="G11" t="n">
+        <v>87.59600905110008</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.573099044536275</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.07108715361251147</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Differential Evolution</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>co2_percent</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>7.42</v>
+      </c>
+      <c r="D12" t="n">
+        <v>9.23441975678467</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1.81441975678467</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.5020118909237635</v>
+      </c>
+      <c r="G12" t="n">
+        <v>87.59600905110008</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.573099044536275</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.07108715361251147</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Differential Evolution</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>carbonated_pH</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>7.63</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-6.08</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.5020118909237635</v>
+      </c>
+      <c r="G13" t="n">
+        <v>87.59600905110008</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.573099044536275</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.07108715361251147</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Differential Evolution</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>sulphited_pH</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>6.95</v>
+      </c>
+      <c r="D14" t="n">
+        <v>11.60661142533998</v>
+      </c>
+      <c r="E14" t="n">
+        <v>4.656611425339983</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.5020118909237635</v>
+      </c>
+      <c r="G14" t="n">
+        <v>87.59600905110008</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.573099044536275</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.07108715361251147</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Differential Evolution</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>sulphited_brix</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>61.67</v>
+      </c>
+      <c r="D15" t="n">
+        <v>44.8</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-16.87</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.5020118909237635</v>
+      </c>
+      <c r="G15" t="n">
+        <v>87.59600905110008</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.573099044536275</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.07108715361251147</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Differential Evolution</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>standard_liquor_pH</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>7.15</v>
+      </c>
+      <c r="D16" t="n">
+        <v>6.446579508458403</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-0.7034204915415971</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.5020118909237635</v>
+      </c>
+      <c r="G16" t="n">
+        <v>87.59600905110008</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.573099044536275</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.07108715361251147</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Differential Evolution</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>standard_liquor_brix</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>54.72</v>
+      </c>
+      <c r="D17" t="n">
+        <v>45.53</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-9.189999999999998</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.5020118909237635</v>
+      </c>
+      <c r="G17" t="n">
+        <v>87.59600905110008</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.573099044536275</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.07108715361251147</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="29" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Method</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Objective</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Current Predicted Value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Recommended Predicted Value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Expected Improvement</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Expected Improvement %</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Bayesian Optimization</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>white_total_points</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>14.5158</v>
+      </c>
+      <c r="D2" t="n">
+        <v>7.544450000000003</v>
+      </c>
+      <c r="E2" t="n">
+        <v>6.971349999999999</v>
+      </c>
+      <c r="F2" t="n">
+        <v>48.0259441436228</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Bayesian Optimization</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>white_solution_color</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>5.132150000000001</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2.731699999999998</v>
+      </c>
+      <c r="E3" t="n">
+        <v>2.400450000000003</v>
+      </c>
+      <c r="F3" t="n">
+        <v>46.7727950274252</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Bayesian Optimization</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>white_apparent_color</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>3.423483333333331</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.584766666666668</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1.838716666666663</v>
+      </c>
+      <c r="F4" t="n">
+        <v>53.70894167246802</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Bayesian Optimization</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>white_ash</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>5.960166666666668</v>
+      </c>
+      <c r="D5" t="n">
+        <v>3.227983333333333</v>
+      </c>
+      <c r="E5" t="n">
+        <v>2.732183333333334</v>
+      </c>
+      <c r="F5" t="n">
+        <v>45.84072033779817</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Differential Evolution</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>white_total_points</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>14.5158</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="E6" t="n">
+        <v>12.6658</v>
+      </c>
+      <c r="F6" t="n">
+        <v>87.25526667493352</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Differential Evolution</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>white_solution_color</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>5.132150000000001</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.6592833333333334</v>
+      </c>
+      <c r="E7" t="n">
+        <v>4.472866666666667</v>
+      </c>
+      <c r="F7" t="n">
+        <v>87.15385689558308</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Differential Evolution</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>white_apparent_color</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>3.423483333333331</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.3759</v>
+      </c>
+      <c r="E8" t="n">
+        <v>3.047583333333331</v>
+      </c>
+      <c r="F8" t="n">
+        <v>89.01995530867683</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Differential Evolution</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>white_ash</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>5.960166666666668</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.8148166666666667</v>
+      </c>
+      <c r="E9" t="n">
+        <v>5.145350000000001</v>
+      </c>
+      <c r="F9" t="n">
+        <v>86.32896171807275</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Observed Min</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Observed Max</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Current Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>lime_milk_baume</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="C2" t="n">
+        <v>2709</v>
+      </c>
+      <c r="D2" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>lime_alkalinity</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3" t="n">
+        <v>13.64</v>
+      </c>
+      <c r="D3" t="n">
+        <v>9.380000000000001</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>co2_percent</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>5.89</v>
+      </c>
+      <c r="C4" t="n">
+        <v>14.31</v>
+      </c>
+      <c r="D4" t="n">
+        <v>7.42</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>carbonated_pH</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="C5" t="n">
+        <v>9.26</v>
+      </c>
+      <c r="D5" t="n">
+        <v>7.63</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>sulphited_pH</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>5.85</v>
+      </c>
+      <c r="C6" t="n">
+        <v>59.26</v>
+      </c>
+      <c r="D6" t="n">
+        <v>6.95</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>sulphited_brix</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>44.8</v>
+      </c>
+      <c r="C7" t="n">
+        <v>670</v>
+      </c>
+      <c r="D7" t="n">
+        <v>61.67</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>standard_liquor_pH</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>5.93</v>
+      </c>
+      <c r="C8" t="n">
+        <v>9.039999999999999</v>
+      </c>
+      <c r="D8" t="n">
+        <v>7.15</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>standard_liquor_brix</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>45.53</v>
+      </c>
+      <c r="C9" t="n">
+        <v>476</v>
+      </c>
+      <c r="D9" t="n">
+        <v>54.72</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="42" customWidth="1" min="5" max="5"/>
+    <col width="42" customWidth="1" min="6" max="6"/>
+    <col width="25" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>created_at_utc</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>historical_rows_used</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>control_variables</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>objectives_minimized</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>constraint</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>current_objective_score</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-06-11 05:10:05 UTC</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>746</v>
+      </c>
+      <c r="D2" t="inlineStr">
         <is>
           <t>lime_milk_baume, lime_alkalinity, co2_percent, carbonated_pH, sulphited_pH, sulphited_brix, standard_liquor_pH, standard_liquor_brix</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>white_total_points, white_solution_color, white_apparent_color, white_ash</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>2026-06-11 04:48:38 UTC</t>
-        </is>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Recommended values are clipped to, and selected inside, observed historical min/max limits.</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>0.573099044536275</v>
       </c>
     </row>
   </sheetData>

--- a/NN/reports/optimization_report.xlsx
+++ b/NN/reports/optimization_report.xlsx
@@ -1506,7 +1506,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-11 05:10:05 UTC</t>
+          <t>2026-06-14 22:03:21 UTC</t>
         </is>
       </c>
       <c r="C2" t="n">

--- a/NN/reports/optimization_report.xlsx
+++ b/NN/reports/optimization_report.xlsx
@@ -1506,7 +1506,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-14 22:03:21 UTC</t>
+          <t>2026-06-15 07:32:33 UTC</t>
         </is>
       </c>
       <c r="C2" t="n">

--- a/NN/reports/optimization_report.xlsx
+++ b/NN/reports/optimization_report.xlsx
@@ -1506,7 +1506,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-15 07:32:33 UTC</t>
+          <t>2026-06-16 14:10:17 UTC</t>
         </is>
       </c>
       <c r="C2" t="n">

--- a/NN/reports/optimization_report.xlsx
+++ b/NN/reports/optimization_report.xlsx
@@ -1506,7 +1506,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-16 14:10:17 UTC</t>
+          <t>2026-06-16 15:30:29 UTC</t>
         </is>
       </c>
       <c r="C2" t="n">

--- a/NN/reports/optimization_report.xlsx
+++ b/NN/reports/optimization_report.xlsx
@@ -1506,7 +1506,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-16 15:30:29 UTC</t>
+          <t>2026-06-16 15:41:45 UTC</t>
         </is>
       </c>
       <c r="C2" t="n">

--- a/NN/reports/optimization_report.xlsx
+++ b/NN/reports/optimization_report.xlsx
@@ -1506,7 +1506,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-16 15:41:45 UTC</t>
+          <t>2026-06-16 16:27:55 UTC</t>
         </is>
       </c>
       <c r="C2" t="n">

--- a/NN/reports/optimization_report.xlsx
+++ b/NN/reports/optimization_report.xlsx
@@ -1506,7 +1506,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-16 16:27:55 UTC</t>
+          <t>2026-06-16 17:02:38 UTC</t>
         </is>
       </c>
       <c r="C2" t="n">

--- a/NN/reports/optimization_report.xlsx
+++ b/NN/reports/optimization_report.xlsx
@@ -1506,7 +1506,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-16 17:02:38 UTC</t>
+          <t>2026-06-16 17:20:49 UTC</t>
         </is>
       </c>
       <c r="C2" t="n">

--- a/NN/reports/optimization_report.xlsx
+++ b/NN/reports/optimization_report.xlsx
@@ -1506,7 +1506,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-16 17:20:49 UTC</t>
+          <t>2026-06-16 18:08:37 UTC</t>
         </is>
       </c>
       <c r="C2" t="n">

--- a/NN/reports/optimization_report.xlsx
+++ b/NN/reports/optimization_report.xlsx
@@ -1506,7 +1506,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-16 18:08:37 UTC</t>
+          <t>2026-06-16 19:00:53 UTC</t>
         </is>
       </c>
       <c r="C2" t="n">

--- a/NN/reports/optimization_report.xlsx
+++ b/NN/reports/optimization_report.xlsx
@@ -1506,7 +1506,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-14 22:03:21 UTC</t>
+          <t>2026-06-16 19:28:00 UTC</t>
         </is>
       </c>
       <c r="C2" t="n">

--- a/NN/reports/optimization_report.xlsx
+++ b/NN/reports/optimization_report.xlsx
@@ -1506,7 +1506,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-16 19:28:00 UTC</t>
+          <t>2026-06-16 20:24:57 UTC</t>
         </is>
       </c>
       <c r="C2" t="n">
